--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488096_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488096_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6297</v>
+        <v>3.7416</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6292</v>
+        <v>1.5273</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0005</v>
+        <v>2.2143</v>
       </c>
       <c r="G2" t="n">
         <v>0.6554</v>
@@ -610,13 +610,13 @@
         <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8287</v>
+        <v>0.9406</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4444</v>
+        <v>0.3425</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3843</v>
+        <v>0.5981</v>
       </c>
       <c r="V2" t="n">
         <v>2.3438</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. HUNT</t>
+          <t>A. BUALO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5677</v>
+        <v>2.3597</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4099</v>
+        <v>3.6847</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-1.325</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7894</v>
+        <v>4.0616</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3608</v>
+        <v>2.7279</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.5714</v>
+        <v>1.3336</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5577</v>
+        <v>6.6993</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6749</v>
+        <v>3.1079</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1172</v>
+        <v>3.5914</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7682</v>
+        <v>-2.6377</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3141</v>
+        <v>-0.38</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4542</v>
+        <v>-2.2577</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1805</v>
+        <v>-4.1627</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1805</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2217</v>
+        <v>-0.3827</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3706</v>
+        <v>-0.3256</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1489</v>
+        <v>-0.0571</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4033</v>
+        <v>1.4737</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4033</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BUALO</t>
+          <t>B. HUNT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4781</v>
+        <v>1.4554</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9716</v>
+        <v>2.4099</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4935</v>
+        <v>-0.9545</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0616</v>
+        <v>1.7894</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7279</v>
+        <v>4.3608</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3336</v>
+        <v>-2.5714</v>
       </c>
       <c r="J4" t="n">
-        <v>6.6993</v>
+        <v>3.5577</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1079</v>
+        <v>4.6749</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5914</v>
+        <v>-1.1172</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6377</v>
+        <v>-1.7682</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.38</v>
+        <v>-0.3141</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2577</v>
+        <v>-1.4542</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1627</v>
+        <v>-2.1805</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5769</v>
+        <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2642</v>
+        <v>-0.334</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0387</v>
+        <v>-0.3706</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2255</v>
+        <v>0.0365</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4737</v>
+        <v>1.4033</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2071</v>
+        <v>-1.4033</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9453</v>
+        <v>1.1761</v>
       </c>
       <c r="E5" t="n">
-        <v>3.123</v>
+        <v>3.1854</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1778</v>
+        <v>-2.0093</v>
       </c>
       <c r="G5" t="n">
         <v>0.6818</v>
@@ -844,13 +844,13 @@
         <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4795</v>
+        <v>0.7103</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3782</v>
+        <v>0.4406</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1013</v>
+        <v>0.2698</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2071</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ ANTUNEZ</t>
+          <t>A. BUALÓ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7609</v>
+        <v>0.6027</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4675</v>
+        <v>0.6027</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7065</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9546</v>
+        <v>0.6027</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8381</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7927</v>
+        <v>0.6027</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4747</v>
+        <v>0.6027</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5782</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.053</v>
+        <v>0.6027</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5201</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2599</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2602</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4871</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.191</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2962</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BUALÓ</t>
+          <t>S. MARTINEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6027</v>
+        <v>0.34</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6027</v>
+        <v>2.9096</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-2.5696</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6027</v>
+        <v>2.2255</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.6634</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6027</v>
+        <v>2.8889</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6027</v>
+        <v>4.624</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.8071</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6027</v>
+        <v>3.8169</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-2.3985</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.4705</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.928</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.0551</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.1881</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2431</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5441</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GUTIERREZ</t>
+          <t>P. FERNANDEZ ANTUNEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.499</v>
+        <v>0.3316</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1528</v>
+        <v>1.1224</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6538</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2255</v>
+        <v>0.9546</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6634</v>
+        <v>-0.8381</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8889</v>
+        <v>1.7927</v>
       </c>
       <c r="J8" t="n">
-        <v>4.624</v>
+        <v>1.4747</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8071</v>
+        <v>-0.5782</v>
       </c>
       <c r="L8" t="n">
-        <v>3.8169</v>
+        <v>2.053</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3985</v>
+        <v>-0.5201</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4705</v>
+        <v>-0.2599</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.928</v>
+        <v>-0.2602</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>0.214</v>
+        <v>0.0578</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0552</v>
+        <v>-0.1541</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1589</v>
+        <v>0.2119</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5441</v>
+        <v>-1.4737</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2071</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. OSORIO HERRERA</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.2222</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1358</v>
+        <v>-0.3353</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1358</v>
+        <v>-0.9764</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.9883</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.9882</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.9765</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1358</v>
+        <v>-1.3237</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1358</v>
+        <v>0.0118</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-1.3355</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1358</v>
+        <v>0.0927</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.0212</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1358</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>A. OSORIO HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1021</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1805</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07829999999999999</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4152</v>
+        <v>0.1358</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6225000000000001</v>
+        <v>0.1358</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7927</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5667</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.968</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5988</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8485</v>
+        <v>0.1358</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3455</v>
+        <v>0.1358</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1939</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.659</v>
+        <v>-0.1358</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1197</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4607</v>
+        <v>-0.1358</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.518</v>
+        <v>-0.5729</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2868</v>
+        <v>-0.7917</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2313</v>
+        <v>0.2187</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3353</v>
+        <v>-2.4152</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9764</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.641</v>
+        <v>-1.7927</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9883</v>
+        <v>-1.5667</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9882</v>
+        <v>-0.968</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9765</v>
+        <v>-0.5988</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3237</v>
+        <v>-0.8485</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0118</v>
+        <v>0.3455</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3355</v>
+        <v>-1.1939</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6475</v>
+        <v>0.1881</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5505</v>
+        <v>0.5085</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0969</v>
+        <v>-0.3203</v>
       </c>
       <c r="V11" t="n">
         <v>0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9207</v>
+        <v>-1.5351</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4662</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9847</v>
+        <v>-1.0689</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6574</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2544</v>
+        <v>0.1313</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7488</v>
+        <v>-0.2789</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4944</v>
+        <v>0.4102</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9136</v>
+        <v>-3.7803</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8506</v>
+        <v>-4.0544</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0629</v>
+        <v>0.274</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0019</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7224</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.121</v>
+        <v>-0.3247</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6014</v>
+        <v>-0.2644</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.028999999999998</v>
+        <v>4.341000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1028</v>
+        <v>10.4147</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.073900000000001</v>
+        <v>-6.073899999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3.696999999999999</v>
@@ -1525,7 +1525,7 @@
         <v>10.3205</v>
       </c>
       <c r="L14" t="n">
-        <v>9.8734</v>
+        <v>9.873399999999998</v>
       </c>
       <c r="M14" t="n">
         <v>-16.497</v>
@@ -1546,19 +1546,19 @@
         <v>15.8578</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4222999999999998</v>
+        <v>0.7342000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6411000000000001</v>
+        <v>-0.3291999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0637</v>
+        <v>1.0635</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.081300000000001</v>
+        <v>-1.0813</v>
       </c>
       <c r="W14" t="n">
-        <v>5.417000000000001</v>
+        <v>5.417</v>
       </c>
       <c r="X14" t="n">
         <v>-6.4983</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5986</v>
+        <v>2.2799</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0462</v>
+        <v>3.2312</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4476</v>
+        <v>-0.9513</v>
       </c>
       <c r="G15" t="n">
         <v>0.5331</v>
@@ -1624,13 +1624,13 @@
         <v>2.9733</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4031</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9877</v>
+        <v>0.1727</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5845</v>
+        <v>-0.0883</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3199</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9595</v>
+        <v>1.8107</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1564</v>
+        <v>1.8107</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8031</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8687</v>
+        <v>1.8107</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3096</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5591</v>
+        <v>1.2053</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6509</v>
+        <v>1.8107</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2447</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4062</v>
+        <v>1.2053</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7822</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9351</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1529</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6674</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5492</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1181</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3873</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8107</v>
+        <v>1.2346</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8107</v>
+        <v>0.2395</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.9951</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8107</v>
+        <v>1.8687</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.3096</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2053</v>
+        <v>1.5591</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8107</v>
+        <v>2.6509</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.2447</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2053</v>
+        <v>1.4062</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.7822</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.9351</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.1529</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.9425</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.6324</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.3101</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3873</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3169</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3556</v>
+        <v>0.6494</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4203</v>
+        <v>0.5221</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.1273</v>
       </c>
       <c r="G18" t="n">
         <v>0.5737</v>
@@ -1858,13 +1858,13 @@
         <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6431</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7012</v>
+        <v>0.8031</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0581</v>
+        <v>0.1339</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2666</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2678</v>
+        <v>0.3753</v>
       </c>
       <c r="E19" t="n">
-        <v>1.573</v>
+        <v>0.3203</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3052</v>
+        <v>0.055</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1398</v>
+        <v>-1.662</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8514</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9912</v>
+        <v>-1.6704</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0302</v>
+        <v>1.1833</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7087</v>
+        <v>1.541</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3214</v>
+        <v>-0.3577</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.17</v>
+        <v>-2.8452</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.5326</v>
       </c>
       <c r="O19" t="n">
         <v>-1.3126</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9822</v>
+        <v>2.5769</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.118</v>
+        <v>0.3056</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0608</v>
+        <v>-0.1384</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9428</v>
+        <v>0.444</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4566</v>
+        <v>0.1459</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.0601</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CASIN LORENTE</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5569</v>
+        <v>-0.0842</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1248</v>
+        <v>1.6748</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4321</v>
+        <v>-1.759</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4695</v>
+        <v>-0.1398</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6052999999999999</v>
+        <v>0.8514</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1358</v>
+        <v>-0.9912</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.0302</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.7087</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.3214</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4695</v>
+        <v>-2.17</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1358</v>
+        <v>-1.3126</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.47</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1248</v>
+        <v>-0.9589</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0374</v>
+        <v>0.4889</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.4566</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.0601</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>J. CASIN LORENTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3928</v>
+        <v>-0.0229</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5301</v>
+        <v>-0.3759</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.662</v>
+        <v>-0.4695</v>
       </c>
       <c r="H21" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6704</v>
+        <v>0.1358</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1833</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.541</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3577</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8452</v>
+        <v>-0.4695</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5326</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3126</v>
+        <v>0.1358</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9926</v>
+        <v>0.0707</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8515</v>
+        <v>-0.0229</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1411</v>
+        <v>0.0936</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1459</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0955</v>
+        <v>-0.9596</v>
       </c>
       <c r="E22" t="n">
         <v>1.7011</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7966</v>
+        <v>-2.6607</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6344</v>
@@ -2170,13 +2170,13 @@
         <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.6681</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6753</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1286</v>
+        <v>0.0072</v>
       </c>
       <c r="V22" t="n">
         <v>1.5411</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5019</v>
+        <v>-1.5862</v>
       </c>
       <c r="E23" t="n">
         <v>-1.2205</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2814</v>
+        <v>-0.3656</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5795</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.0156</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3182</v>
+        <v>0.234</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1812</v>
+        <v>-2.0454</v>
       </c>
       <c r="E24" t="n">
         <v>0.1387</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.32</v>
+        <v>-2.1841</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2244</v>
@@ -2326,13 +2326,13 @@
         <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4295</v>
+        <v>-0.2937</v>
       </c>
       <c r="T24" t="n">
         <v>-0.301</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1286</v>
+        <v>0.0072</v>
       </c>
       <c r="V24" t="n">
         <v>0.0674</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7627</v>
+        <v>-3.9465</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0343</v>
+        <v>-2.3212</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7284</v>
+        <v>-1.6252</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7736</v>
@@ -2404,13 +2404,13 @@
         <v>2.9733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7732</v>
+        <v>0.0431</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0387</v>
+        <v>-0.3256</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2655</v>
+        <v>0.3687</v>
       </c>
       <c r="V25" t="n">
         <v>1.7573</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.0289</v>
+        <v>-2.670799999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>6.074000000000002</v>
+        <v>6.073800000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.103</v>
+        <v>-8.744399999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.697000000000001</v>
+        <v>-3.697</v>
       </c>
       <c r="H26" t="n">
         <v>-5.0838</v>
@@ -2482,13 +2482,13 @@
         <v>14.8666</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4224</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0636</v>
+        <v>-1.0635</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6410999999999998</v>
+        <v>1.9993</v>
       </c>
       <c r="V26" t="n">
         <v>1.0813</v>
@@ -2497,7 +2497,7 @@
         <v>6.4984</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.4169</v>
+        <v>-5.416899999999999</v>
       </c>
     </row>
   </sheetData>
